--- a/EjemploPruebasFuncionales.xlsx
+++ b/EjemploPruebasFuncionales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csimon\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Megu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64DBF675-A420-41FC-961E-754578F6A1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80ADD71-3AF8-478A-A1BB-775B5DB10B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3855" yWindow="3030" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas Unitarias" sheetId="6" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="Caso 2" sheetId="9" r:id="rId3"/>
     <sheet name="Caso X" sheetId="10" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -260,11 +257,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#"/>
-    <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,21 +326,9 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFA4405"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFA4405"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -374,7 +358,21 @@
       <sz val="24"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="2"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -386,7 +384,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFA4405"/>
+        <fgColor theme="1" tint="0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -739,7 +737,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2">
       <alignment wrapText="1"/>
@@ -755,41 +753,29 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -798,35 +784,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -836,6 +808,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -843,21 +854,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -866,35 +862,28 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -919,68 +908,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>277019</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>154781</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image2.jpg">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect l="176" r="176"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="3464719" cy="1321594"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Caso 0"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1281,7 +1208,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A5:F49"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.5703125" style="1" customWidth="1"/>
@@ -1292,121 +1219,121 @@
     <col min="7" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:6">
-      <c r="A5" s="42" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="43"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-    </row>
-    <row r="8" spans="1:6" ht="12.95" thickBot="1">
-      <c r="A8" s="43"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-    </row>
-    <row r="9" spans="1:6" ht="12.95" thickBot="1">
-      <c r="A9" s="44" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="54"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="54"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+    </row>
+    <row r="8" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="54"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+    </row>
+    <row r="9" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
-    </row>
-    <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="7" t="s">
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="45"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="50"/>
-    </row>
-    <row r="11" spans="1:6" ht="21" customHeight="1">
-      <c r="A11" s="8" t="s">
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="32"/>
+    </row>
+    <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="53"/>
-    </row>
-    <row r="12" spans="1:6" ht="12.75">
-      <c r="A12" s="8" t="s">
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="35"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="41"/>
-    </row>
-    <row r="13" spans="1:6" ht="12.6" customHeight="1">
-      <c r="A13" s="8" t="s">
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="29"/>
+    </row>
+    <row r="13" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="41"/>
-    </row>
-    <row r="14" spans="1:6" ht="20.25">
-      <c r="A14" s="8" t="s">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="29"/>
+    </row>
+    <row r="14" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="26"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="8" t="s">
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="29"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="26"/>
-    </row>
-    <row r="16" spans="1:6" ht="12.75">
-      <c r="A16" s="8" t="s">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="29"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="29"/>
-    </row>
-    <row r="17" spans="1:6" ht="12.95" thickBot="1">
+      <c r="B16" s="36"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="38"/>
+    </row>
+    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
@@ -1414,302 +1341,322 @@
       <c r="E17" s="6"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="12.95" thickBot="1">
-      <c r="A18" s="30" t="s">
+    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
-    </row>
-    <row r="19" spans="1:6" ht="12.75">
-      <c r="A19" s="9" t="s">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="50"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="52" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15">
-      <c r="A20" s="36" t="s">
+    <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="E20" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="F20" s="23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A21" s="37"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="18" t="s">
+    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="40"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-    </row>
-    <row r="22" spans="1:6" ht="15">
-      <c r="A22" s="37"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="19" t="s">
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="40"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-    </row>
-    <row r="23" spans="1:6" ht="12.75">
-      <c r="A23" s="37"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="20" t="s">
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="40"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-    </row>
-    <row r="24" spans="1:6" ht="12.75">
-      <c r="A24" s="38"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-    </row>
-    <row r="25" spans="1:6" ht="15">
-      <c r="A25" s="55" t="s">
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="41"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+    </row>
+    <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-    </row>
-    <row r="26" spans="1:6" ht="15">
-      <c r="A26" s="55"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-    </row>
-    <row r="27" spans="1:6" ht="15">
-      <c r="A27" s="55"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A28" s="55"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1">
-      <c r="A29" s="55"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-    </row>
-    <row r="30" spans="1:6" ht="13.15" customHeight="1">
-      <c r="A30" s="55" t="s">
+      <c r="C25" s="11"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+    </row>
+    <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="26"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+    </row>
+    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="26"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="26"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+    </row>
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="26"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+    </row>
+    <row r="30" spans="1:6" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="54"/>
-    </row>
-    <row r="31" spans="1:6" ht="13.15" customHeight="1">
-      <c r="A31" s="55"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-    </row>
-    <row r="32" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A32" s="55"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-    </row>
-    <row r="33" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A33" s="55"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-    </row>
-    <row r="34" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A34" s="55"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1">
-      <c r="A35" s="23"/>
-      <c r="B35" s="22"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+    </row>
+    <row r="31" spans="1:6" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="26"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+    </row>
+    <row r="32" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="26"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+    </row>
+    <row r="33" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="26"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+    </row>
+    <row r="34" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="26"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+    </row>
+    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="20"/>
+      <c r="B35" s="21"/>
       <c r="C35"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-    </row>
-    <row r="36" spans="1:6" ht="15">
-      <c r="A36" s="23"/>
-      <c r="B36" s="22"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+    </row>
+    <row r="36" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A36" s="20"/>
+      <c r="B36" s="21"/>
       <c r="C36"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-    </row>
-    <row r="37" spans="1:6" ht="15">
-      <c r="A37" s="23"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-    </row>
-    <row r="38" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A38" s="23"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-    </row>
-    <row r="39" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A39" s="23"/>
-      <c r="B39" s="22"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+    </row>
+    <row r="37" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A37" s="20"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+    </row>
+    <row r="38" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="20"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+    </row>
+    <row r="39" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="20"/>
+      <c r="B39" s="21"/>
       <c r="C39"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-    </row>
-    <row r="40" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A40" s="23"/>
-      <c r="B40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-    </row>
-    <row r="41" spans="1:6" ht="12.75">
-      <c r="A41" s="23"/>
-      <c r="B41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-    </row>
-    <row r="42" spans="1:6" ht="15">
-      <c r="A42" s="23"/>
-      <c r="B42" s="22"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+    </row>
+    <row r="40" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="20"/>
+      <c r="B40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="20"/>
+      <c r="B41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+    </row>
+    <row r="42" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42" s="20"/>
+      <c r="B42" s="21"/>
       <c r="C42"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-    </row>
-    <row r="43" spans="1:6" ht="12.6" customHeight="1">
-      <c r="A43" s="23"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-    </row>
-    <row r="44" spans="1:6" ht="12.6" customHeight="1">
-      <c r="A44" s="23"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-    </row>
-    <row r="45" spans="1:6" ht="12.6" customHeight="1">
-      <c r="A45" s="23"/>
-      <c r="B45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-    </row>
-    <row r="46" spans="1:6" ht="12.6" customHeight="1">
-      <c r="A46" s="23"/>
-      <c r="B46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-    </row>
-    <row r="47" spans="1:6" ht="12.75">
-      <c r="A47" s="23"/>
-      <c r="B47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-    </row>
-    <row r="48" spans="1:6" ht="12.75">
-      <c r="A48" s="23"/>
-      <c r="B48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-    </row>
-    <row r="49" spans="1:6" ht="12.75">
-      <c r="A49" s="23"/>
-      <c r="B49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+    </row>
+    <row r="43" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="20"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+    </row>
+    <row r="44" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="20"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+    </row>
+    <row r="45" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="20"/>
+      <c r="B45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+    </row>
+    <row r="46" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="20"/>
+      <c r="B46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="20"/>
+      <c r="B47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="20"/>
+      <c r="B48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="20"/>
+      <c r="B49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="D35:D39"/>
-    <mergeCell ref="E35:E39"/>
-    <mergeCell ref="F35:F39"/>
+    <mergeCell ref="F45:F49"/>
+    <mergeCell ref="E45:E49"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="B45:B49"/>
+    <mergeCell ref="D45:D49"/>
+    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="E40:E44"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="E20:E24"/>
+    <mergeCell ref="F20:F24"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="D20:D24"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="A5:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="D25:D29"/>
     <mergeCell ref="B25:B29"/>
     <mergeCell ref="A25:A29"/>
@@ -1720,33 +1667,13 @@
     <mergeCell ref="D30:D34"/>
     <mergeCell ref="F25:F29"/>
     <mergeCell ref="E25:E29"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A5:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="E20:E24"/>
-    <mergeCell ref="F20:F24"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="D20:D24"/>
-    <mergeCell ref="A40:A44"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="D40:D44"/>
-    <mergeCell ref="E40:E44"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="F45:F49"/>
-    <mergeCell ref="E45:E49"/>
-    <mergeCell ref="A45:A49"/>
-    <mergeCell ref="B45:B49"/>
-    <mergeCell ref="D45:D49"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="B35:B39"/>
+    <mergeCell ref="D35:D39"/>
+    <mergeCell ref="E35:E39"/>
+    <mergeCell ref="F35:F39"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A25" location="'Caso 0'!A1" display="Caso 0" xr:uid="{D596BA7A-75FD-4B75-8038-B2B966C159D3}"/>
     <hyperlink ref="A25:A29" location="'Caso 1'!A1" display="Caso 1" xr:uid="{C5458276-3A0F-43FA-A1DF-D1A81C4BFA5E}"/>
@@ -1756,197 +1683,196 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1ECDA97-B170-4D31-92F2-BBEDE209DAAD}">
   <dimension ref="A2:J16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:10">
-      <c r="A2" s="56" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="57"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="57"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="57"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="57"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="57"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="57"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="57"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="57"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="57"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="57"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1959,189 +1885,189 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52669F79-AD6C-46CE-B1DF-A724ADB6B01C}">
   <dimension ref="A2:J16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:10">
-      <c r="A2" s="56" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="57"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="57"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="57"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="57"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="57"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="57"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="57"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="57"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="57"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="57"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2154,189 +2080,189 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42408E20-1CBD-4BDB-B951-D9C111585262}">
   <dimension ref="A2:J16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:10">
-      <c r="A2" s="56" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="57"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="57"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="57"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="57"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="57"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="57"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="57"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="57"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="57"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="57"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
